--- a/data/b2_centro/B2 Centro 12-2025.xlsx
+++ b/data/b2_centro/B2 Centro 12-2025.xlsx
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>77290.24000000001</v>
+        <v>77306.23</v>
       </c>
     </row>
     <row r="3">
@@ -5044,25 +5044,25 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>6531.39</v>
+        <v>6338.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>3350.53</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="5">
@@ -5071,21 +5071,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>38000</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -5094,142 +5094,142 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3216.82</v>
+        <v>4409.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>4300</v>
+        <v>2005.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46002</v>
+        <v>46005</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1533.49</v>
+        <v>6678.19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1897.32</v>
+        <v>14862.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1877.94</v>
+        <v>4922.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46005</v>
+        <v>46007</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>6355.13</v>
+        <v>3385.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>15577.58</v>
+        <v>2076.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>3936.36</v>
+        <v>2347.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -5238,11 +5238,11 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1187.88</v>
+        <v>1894.71</v>
       </c>
     </row>
     <row r="15">
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>27288.63</v>
+        <v>27579.84</v>
       </c>
     </row>
     <row r="16">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>6019.1</v>
+        <v>5922.28</v>
       </c>
     </row>
     <row r="17">
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>6142.43</v>
+        <v>5959.79</v>
       </c>
     </row>
     <row r="18">
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2551.82</v>
+        <v>2541.66</v>
       </c>
     </row>
   </sheetData>
